--- a/V54_RESET/source_data/V54_RESET_par_data.xlsx
+++ b/V54_RESET/source_data/V54_RESET_par_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interainc-my.sharepoint.com/personal/mearll_intera_com/Documents/Models/DWR_Contract/Long_term_sites_data/00_Model_Input_files/V 54 RESET/source_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mearll\Documents\GitHub\1D_CSUB\V54_RESETshallow\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{5485C3FF-4C29-5A4F-8F28-53C994EDAE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6407ECD1-E41C-408A-8F2D-67765C0D14F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9B9A92-6A20-4233-8EA8-6C17DA6DA532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="615" windowWidth="15765" windowHeight="15585" xr2:uid="{5DFCA8DB-E838-45AE-8EA2-ACBA3F797179}"/>
+    <workbookView xWindow="7860" yWindow="1920" windowWidth="19005" windowHeight="15585" xr2:uid="{5DFCA8DB-E838-45AE-8EA2-ACBA3F797179}"/>
   </bookViews>
   <sheets>
     <sheet name="G158_RESET" sheetId="1" r:id="rId1"/>
@@ -209,11 +209,11 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M2">
         <f>C4</f>
-        <v>1490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>1490</v>
+        <v>690</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -1839,15 +1839,15 @@
       <c r="J7" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="8">
         <f>2.3*10^-4</f>
         <v>2.2999999999999998E-4</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <f>2.3*10^-4</f>
         <v>2.2999999999999998E-4</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <f>2.3*10^-4</f>
         <v>2.2999999999999998E-4</v>
       </c>
@@ -1858,36 +1858,36 @@
       <c r="J8" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="8">
         <f>0.0000028</f>
         <v>2.7999999999999999E-6</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <f>0.0000028</f>
         <v>2.7999999999999999E-6</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <f>0.0000028</f>
         <v>2.7999999999999999E-6</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
       <c r="J9" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>0.4</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>0.4</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <v>0.4</v>
       </c>
     </row>
@@ -1896,13 +1896,13 @@
       <c r="J10" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
         <v>1.5200000000000001E-3</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>1.5200000000000001E-3</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <v>1.5200000000000001E-3</v>
       </c>
     </row>
@@ -1913,13 +1913,13 @@
       <c r="J11" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="9">
         <v>0</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <v>0</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="9">
         <v>0</v>
       </c>
     </row>
